--- a/CBT_2021_4회/산업안전기사_2021_4회_문항등록.xlsx
+++ b/CBT_2021_4회/산업안전기사_2021_4회_문항등록.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="문항등록" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용가이드" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="커리큘럼ID" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="색상범례" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="문항등록" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="사용가이드" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="커리큘럼ID" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="색상범례" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1963,17 +1963,17 @@
       </c>
       <c r="AG7" s="32" t="inlineStr">
         <is>
-          <t>3R 은 &lt;strong&gt;대책수립&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;위험예지훈련의 4라운드&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;라운드&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;이름&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1R&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;현상파악&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;어떤 위험이 숨어 있나&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2R&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;본질추구&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이것이 위험의 요점이다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;3R&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;대책수립&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;당신이라면 어떻게 하겠는가&lt;/u&gt; · 이 문항&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;4R&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;목표설정&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;우리는 이렇게 한다&lt;/u&gt; · 지적확인&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>3R은 &lt;strong&gt;대책수립&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;위험예지훈련의 4라운드&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;라운드&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;이름&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1R&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;현상파악&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;어떤 위험이 숨어 있나&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2R&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;본질추구&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이것이 위험의 요점이다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;3R&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;대책수립&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;당신이라면 어떻게 하겠는가&lt;/u&gt; · 이 문항&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;4R&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;목표설정&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;우리는 이렇게 한다&lt;/u&gt; · 지적확인&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH7" s="32" t="inlineStr">
         <is>
-          <t>① 목표설정은 4R 이다.&lt;br&gt;③ 본질추구는 2R 이다.&lt;br&gt;④ 현상파악은 1R 이다.</t>
+          <t>① 목표설정은 4R이다.&lt;br&gt;③ 본질추구는 2R이다.&lt;br&gt;④ 현상파악은 1R이다.</t>
         </is>
       </c>
       <c r="AI7" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;위험예지훈련의 4라운드&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「보고(현상) → 짚고(본질) → 세우고(대책) → 다짐한다(목표)」&lt;/strong&gt; 순이다 — &lt;strong&gt;대책이 목표보다 앞&lt;/strong&gt;이라는 것만 잡으면 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;3R 은 대책수립&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;위험예지훈련의 4라운드&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「보고(현상) → 짚고(본질) → 세우고(대책) → 다짐한다(목표)」&lt;/strong&gt; 순이다 — &lt;strong&gt;대책이 목표보다 앞&lt;/strong&gt;이라는 것만 잡으면 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;3R은 대책수립&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -2221,17 +2221,17 @@
       </c>
       <c r="AG9" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;B 는 Behavior, 곧 행동&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;레빈(Lewin)의 법칙&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기호&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;뜻&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보기&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;B&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Behavior — 인간의 행동&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;f&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;function — 함수관계&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;P&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Person — 사람의 조건&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;연령 · 성격 · 지능 · 소질 · 경험&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;E&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Environment — 환경 조건&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;작업환경 · 인간관계 · 설비적 결함&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;B는 Behavior, 곧 행동&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;레빈(Lewin)의 법칙&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기호&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;뜻&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보기&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;B&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Behavior — 인간의 행동&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;f&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;function — 함수관계&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;P&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Person — 사람의 조건&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;연령 · 성격 · 지능 · 소질 · 경험&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;E&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Environment — 환경 조건&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;작업환경 · 인간관계 · 설비적 결함&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH9" s="32" t="inlineStr">
         <is>
-          <t>① 인간관계는 E 에 드는 조건이다.&lt;br&gt;③ 환경은 E 다.&lt;br&gt;④ 함수는 f 다.</t>
+          <t>① 인간관계는 E에 드는 조건이다.&lt;br&gt;③ 환경은 E다.&lt;br&gt;④ 함수는 f다.</t>
         </is>
       </c>
       <c r="AI9" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;레빈의 법칙&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;네 보기가 B · f · P · E 에 하나씩&lt;/strong&gt; 걸린다 — &lt;strong&gt;Behavior 의 첫 글자가 B&lt;/strong&gt;라는 것으로 곧장 풀린다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;B 는 Behavior, 곧 행동&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;레빈의 법칙&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;네 보기가 B · f · P · E에 하나씩&lt;/strong&gt; 걸린다 — &lt;strong&gt;Behavior의 첫 글자가 B&lt;/strong&gt;라는 것으로 곧장 풀린다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;B는 Behavior, 곧 행동&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="AH11" s="32" t="inlineStr">
         <is>
-          <t>① 교차점을 위험일이라 하는 것은 맞다.&lt;br&gt;② 육체적 리듬의 설명도 맞다.&lt;br&gt;③ 지성적 리듬을 I 로 표시하는 것도 맞다.</t>
+          <t>① 교차점을 위험일이라 하는 것은 맞다.&lt;br&gt;② 육체적 리듬의 설명도 맞다.&lt;br&gt;③ 지성적 리듬을 I로 표시하는 것도 맞다.</t>
         </is>
       </c>
       <c r="AI11" s="32" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="AG15" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;심포지엄&lt;/strong&gt;이다. &lt;strong&gt;여러 전문가가 발표한 뒤 청중이 질문&lt;/strong&gt; 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;토의식 교육의 갈래&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;방법&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;심포지엄&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;몇 사람의 전문가가 발표한 뒤 청중이 의견을 내거나 질문한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;포럼&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;사회자가 짧게 문제를 던지고 청중이 토의하며 결론을 낸다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;패널 디스커션&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;4 ~ 5명의 패널이 토의한 뒤 청중과 질의응답&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;버즈 세션&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;6명씩 나눠 6분간 토의&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;6-6 회의&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;자유토의법&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;주제를 놓고 자유롭게&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;심포지엄&lt;/strong&gt;이다. &lt;strong&gt;여러 전문가가 발표한 뒤 청중이 질문&lt;/strong&gt;한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;토의식 교육의 갈래&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;방법&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;심포지엄&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;몇 사람의 전문가가 발표한 뒤 청중이 의견을 내거나 질문한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;포럼&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;사회자가 짧게 문제를 던지고 청중이 토의하며 결론을 낸다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;패널 디스커션&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;4 ~ 5명의 패널이 토의한 뒤 청중과 질의응답&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;버즈 세션&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;6명씩 나눠 6분간 토의&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;6-6 회의&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;자유토의법&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;주제를 놓고 자유롭게&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH15" s="32" t="inlineStr">
@@ -3093,7 +3093,11 @@
           <t>재해사례연구 순서로 옳은 것은?</t>
         </is>
       </c>
-      <c r="V16" s="32" t="inlineStr"/>
+      <c r="V16" s="32" t="inlineStr">
+        <is>
+          <t>재해 상황의 파악 → ( ㉠ ) → ( ㉡ ) → 근본적 문제점의 결정 → ( ㉢ )</t>
+        </is>
+      </c>
       <c r="W16" s="32" t="inlineStr"/>
       <c r="X16" s="32" t="inlineStr">
         <is>
@@ -3521,7 +3525,7 @@
       </c>
       <c r="AI19" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;하인리히의 재해구성비율&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;중상 1 에 경상 29&lt;/strong&gt; 이니 &lt;strong&gt;중상이 2 면 경상은 58&lt;/strong&gt;이다 — &lt;strong&gt;600 은 무상해 쪽&lt;/strong&gt;이라 자리를 헷갈리게 놓았다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;하인리히 1 : 29 : 300&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;하인리히의 재해구성비율&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;중상 1에 경상 29&lt;/strong&gt; 이니 &lt;strong&gt;중상이 2 면 경상은 58&lt;/strong&gt;이다 — &lt;strong&gt;600은 무상해 쪽&lt;/strong&gt;이라 자리를 헷갈리게 놓았다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;하인리히 1 : 29 : 300&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4035,7 @@
       </c>
       <c r="AG23" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;톱사상의 선정&lt;/strong&gt;이 먼저다. &lt;strong&gt;무엇을 분석할지부터 정한다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;FTA 에 의한 재해사례 연구 순서&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;이름&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;톱(TOP)사상의 선정&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;분석할 정상사상을 정한다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;사상의 재해 원인 규명&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;각 사상의 원인을 조사한다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;3&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;FT도의 작성&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;논리기호로 그린다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;개선 계획의 작성&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;대책을 세운다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;개선안 실시계획&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;톱사상의 선정&lt;/strong&gt;이 먼저다. &lt;strong&gt;무엇을 분석할지부터 정한다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;FTA에 의한 재해사례 연구 순서&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;이름&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;톱(TOP)사상의 선정&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;분석할 정상사상을 정한다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;사상의 재해 원인 규명&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;각 사상의 원인을 조사한다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;3&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;FT도의 작성&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;논리기호로 그린다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;개선 계획의 작성&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;대책을 세운다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;개선안 실시계획&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH23" s="32" t="inlineStr">
@@ -4041,7 +4045,7 @@
       </c>
       <c r="AI23" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;FTA 의 진행 순서&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;FTA 는 「꼭대기에서 아래로」 내려가는 방법&lt;/strong&gt;이다 — &lt;strong&gt;꼭대기(톱사상)를 정하지 않으면 시작할 수가 없다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;FTA 는 톱사상의 선정부터&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;FTA의 진행 순서&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;FTA는 「꼭대기에서 아래로」 내려가는 방법&lt;/strong&gt;이다 — &lt;strong&gt;꼭대기(톱사상)를 정하지 않으면 시작할 수가 없다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;FTA는 톱사상의 선정부터&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4259,7 +4263,7 @@
       </c>
       <c r="U25" s="32" t="inlineStr">
         <is>
-          <t>다음 중 인간 에러 (human error) 에 관한 설명으로 틀린 것은?</t>
+          <t>다음 중 인간 에러 (human error)에 관한 설명으로 틀린 것은?</t>
         </is>
       </c>
       <c r="V25" s="32" t="inlineStr"/>
@@ -4293,17 +4297,17 @@
       </c>
       <c r="AG25" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;수행 지연은 timing error&lt;/strong&gt;다. &lt;strong&gt;commission error 는 「하기는 했으나 잘못한」&lt;/strong&gt; 것이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;스웨인(Swain)의 심리적 분류&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;오류&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;omission error&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;해야 할 것을 하지 않았다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;생략 오류&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;commission error&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;했지만 잘못했다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「수행 지연」이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;timing error&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;너무 이르거나 늦었다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;②가 설명한 것&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;sequential error&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;순서를 틀렸다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;extraneous error&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;하지 않아도 될 일을 했다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;수행 지연은 timing error&lt;/strong&gt;다. &lt;strong&gt;commission error는 「하기는 했으나 잘못한」&lt;/strong&gt; 것이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;스웨인(Swain)의 심리적 분류&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;오류&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;omission error&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;해야 할 것을 하지 않았다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;생략 오류&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;commission error&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;했지만 잘못했다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「수행 지연」이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;timing error&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;너무 이르거나 늦었다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;②가 설명한 것&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;sequential error&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;순서를 틀렸다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;extraneous error&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;하지 않아도 될 일을 했다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH25" s="32" t="inlineStr">
         <is>
-          <t>① omission error 의 설명은 옳다.&lt;br&gt;③ extraneous error 의 설명도 옳다.&lt;br&gt;④ sequential error 의 설명도 옳다.</t>
+          <t>① omission error의 설명은 옳다.&lt;br&gt;③ extraneous error의 설명도 옳다.&lt;br&gt;④ sequential error의 설명도 옳다.</t>
         </is>
       </c>
       <c r="AI25" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;휴먼 에러의 분류&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;다섯 가운데 「시간」에 관한 것이 timing error 하나&lt;/strong&gt;다 — &lt;strong&gt;「지연」이라는 낱말이 나왔는데 commission 이라 적혀 있으면&lt;/strong&gt; 틀린 것이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;수행 지연은 timing error&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;휴먼 에러의 분류&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;다섯 가운데 「시간」에 관한 것이 timing error 하나&lt;/strong&gt;다 — &lt;strong&gt;「지연」이라는 낱말이 나왔는데 commission이라 적혀 있으면&lt;/strong&gt; 틀린 것이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;수행 지연은 timing error&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4424,7 +4428,7 @@
       </c>
       <c r="AI26" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;인간과 기계의 기능 비교&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;인간은 「애매한 것을 알아채고 미루어 짐작하는」 데 낫고, 기계는 「많이 · 빨리 · 똑같이」&lt;/strong&gt; 하는 데 낫다 — &lt;strong&gt;「대량 · 신속 · 보관」이라는 낱말은 기계 쪽&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;대량·신속한 정보 보관은 기계가 우수&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;인간과 기계의 기능 비교&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;인간은 「애매한 것을 알아채고 미루어 짐작하는」 데 낫고, 기계는 「많이 · 빨리 · 똑같이」&lt;/strong&gt;하는 데 낫다 — &lt;strong&gt;「대량 · 신속 · 보관」이라는 낱말은 기계 쪽&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;대량·신속한 정보 보관은 기계가 우수&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4553,7 +4557,7 @@
       </c>
       <c r="AI27" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;유해위험방지계획서의 제출&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「제조는 15일 전, 건설은 착공 전날」&lt;/strong&gt;로 갈린다 — &lt;strong&gt;심사 통보도 15일 이내&lt;/strong&gt;라 15 라는 수가 두 번 나온다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;제조업은 작업 시작 15일 전까지&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;유해위험방지계획서의 제출&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「제조는 15일 전, 건설은 착공 전날」&lt;/strong&gt;로 갈린다 — &lt;strong&gt;심사 통보도 15일 이내&lt;/strong&gt;라 15라는 수가 두 번 나온다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;제조업은 작업 시작 15일 전까지&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4922,12 +4926,12 @@
       </c>
       <c r="AG30" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;운전단계&lt;/strong&gt;다. &lt;strong&gt;실제로 돌려 보며 평가&lt;/strong&gt; 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;시스템의 수명주기 5단계&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;이름&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;구상단계&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;PHA · 안전성 기준 설정&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정의(사양결정)단계&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;안전성 유무 판단 · 시스템 안전 요구사항&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;3&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;개발(설계)단계&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;FHA · FMEA · 안전성 확인&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;생산(제조)단계&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;제조·조립 과정의 안전&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;운전(배치와 운용)단계&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안전점검 기준에 따른 평가&lt;/u&gt; · 이 문항&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;운전단계&lt;/strong&gt;다. &lt;strong&gt;실제로 돌려 보며 평가&lt;/strong&gt;한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;시스템의 수명주기 5단계&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;이름&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;구상단계&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;PHA · 안전성 기준 설정&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정의(사양결정)단계&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;안전성 유무 판단 · 시스템 안전 요구사항&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;3&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;개발(설계)단계&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;FHA · FMEA · 안전성 확인&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;생산(제조)단계&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;제조·조립 과정의 안전&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;운전(배치와 운용)단계&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안전점검 기준에 따른 평가&lt;/u&gt; · 이 문항&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH30" s="32" t="inlineStr">
         <is>
-          <t>① 구상단계에서는 PHA 를 한다.&lt;br&gt;② 설계단계에서는 FHA·FMEA 를 한다.&lt;br&gt;③ 생산단계는 제조·조립 과정의 안전을 다룬다.</t>
+          <t>① 구상단계에서는 PHA를 한다.&lt;br&gt;② 설계단계에서는 FHA·FMEA를 한다.&lt;br&gt;③ 생산단계는 제조·조립 과정의 안전을 다룬다.</t>
         </is>
       </c>
       <c r="AI30" s="32" t="inlineStr">
@@ -5185,7 +5189,7 @@
       </c>
       <c r="AH32" s="32" t="inlineStr">
         <is>
-          <t>① 누락 오류는 아예 하지 않은 경우다.&lt;br&gt;② 기계 고장이 아니므로 fail safe 가 아니다.&lt;br&gt;③ 오류의 종류와 설계원칙이 모두 어긋난 조합이다.</t>
+          <t>① 누락 오류는 아예 하지 않은 경우다.&lt;br&gt;② 기계 고장이 아니므로 fail safe가 아니다.&lt;br&gt;③ 오류의 종류와 설계원칙이 모두 어긋난 조합이다.</t>
         </is>
       </c>
       <c r="AI32" s="32" t="inlineStr">
@@ -5313,12 +5317,12 @@
       </c>
       <c r="AG33" s="32" t="inlineStr">
         <is>
-          <t>R 두 개가 &lt;strong&gt;병렬&lt;/strong&gt;, 그 묶음과 M 이 &lt;strong&gt;직렬&lt;/strong&gt;이다.$R_{(\text{전체})} = {1 - ( 1 - R )^{2}} \times M = ( 2 R - R^{2} ) M = M ( 2 R - R^{2} )$&lt;div style="margin:12px 0 2px;font-weight:700"&gt;직·병렬 조합&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;R ∥ R&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$1 - ( 1 - R )^{2} = 2 R - R^{2}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;M 과 직렬&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$( 2 R - R^{2} ) \times M$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;④&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;검산 (R = 0.9, M = 0.9)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;(1.8 − 0.81) × 0.9 = 0.891&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;한 개짜리보다 낮다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>R 두 개가 &lt;strong&gt;병렬&lt;/strong&gt;, 그 묶음과 M이 &lt;strong&gt;직렬&lt;/strong&gt;이다.$R_{(\text{전체})} = {1 - ( 1 - R )^{2}} \times M = ( 2 R - R^{2} ) M = M ( 2 R - R^{2} )$&lt;div style="margin:12px 0 2px;font-weight:700"&gt;직·병렬 조합&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;R ∥ R&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$1 - ( 1 - R )^{2} = 2 R - R^{2}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;M과 직렬&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$( 2 R - R^{2} ) \times M$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;④&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;검산 (R = 0.9, M = 0.9)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;(1.8 − 0.81) × 0.9 = 0.891&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;한 개짜리보다 낮다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH33" s="32" t="inlineStr">
         <is>
-          <t>① MR³ 은 세 요소를 모두 직렬로 본 꼴이다.&lt;br&gt;② R²(1−MR) 은 병렬 계산을 잘못한 것이다.&lt;br&gt;③ M(R²+R)−1 은 물리적 뜻이 없는 꼴이다.</t>
+          <t>① MR³ 은 세 요소를 모두 직렬로 본 꼴이다.&lt;br&gt;② R²(1−MR)은 병렬 계산을 잘못한 것이다.&lt;br&gt;③ M(R²+R)−1은 물리적 뜻이 없는 꼴이다.</t>
         </is>
       </c>
       <c r="AI33" s="32" t="inlineStr">
@@ -5963,12 +5967,12 @@
       </c>
       <c r="AH38" s="32" t="inlineStr">
         <is>
-          <t>② FMEA 는 설비의 고장을 분석하는 기법이다.&lt;br&gt;③ OSHA 는 기관 이름이지 기법이 아니다.&lt;br&gt;④ MORT 는 관리 전반을 다루는 프로그램이다.</t>
+          <t>② FMEA는 설비의 고장을 분석하는 기법이다.&lt;br&gt;③ OSHA는 기관 이름이지 기법이 아니다.&lt;br&gt;④ MORT는 관리 전반을 다루는 프로그램이다.</t>
         </is>
       </c>
       <c r="AI38" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;THERP&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;THERP 는 Technique for Human Error Rate Prediction&lt;/strong&gt; — &lt;strong&gt;이름에 Human Error Rate 가 그대로 들어 있다&lt;/strong&gt;. &lt;strong&gt;「사람의 실수 확률」을 물으면 THERP&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;사람의 실수 확률 예측은 THERP&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;THERP&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;THERP는 Technique for Human Error Rate Prediction&lt;/strong&gt; — &lt;strong&gt;이름에 Human Error Rate가 그대로 들어 있다&lt;/strong&gt;. &lt;strong&gt;「사람의 실수 확률」을 물으면 THERP&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;사람의 실수 확률 예측은 THERP&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6216,7 +6220,7 @@
       </c>
       <c r="AG40" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;「작업 조건의 평가」&lt;/strong&gt;라는 단계는 없다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전성 평가의 6단계&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;이름&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;관계 자료의 정비검토&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정성적 평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;입지조건 · 배치 · 건조물 · 공정&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;3&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정량적 평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;물 · 용 · 온 · 압 · 조&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안전대책&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;설비 대책 · 관리적 대책&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;재해정보에 의한 재평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;6&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;FTA 에 의한 재평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;「작업 조건의 평가」&lt;/strong&gt;라는 단계는 없다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전성 평가의 6단계&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;이름&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;관계 자료의 정비검토&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정성적 평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;입지조건 · 배치 · 건조물 · 공정&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;3&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정량적 평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;물 · 용 · 온 · 압 · 조&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안전대책&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;설비 대책 · 관리적 대책&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;재해정보에 의한 재평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;6&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;FTA에 의한 재평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH40" s="32" t="inlineStr">
@@ -6736,17 +6740,17 @@
       </c>
       <c r="AG44" s="32" t="inlineStr">
         <is>
-          <t>$$V = \dfrac{\pi D N}{1 {,} 000} = \dfrac{\pi \times 200 \times 3 {,} 600}{1 {,} 000} \fallingdotseq 2 {,} 262 \, m / \mathrm{min}$$&lt;div style="margin:12px 0 2px;font-weight:700"&gt;원주속도의 계산&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$V = \dfrac{\pi D N}{1 {,} 000} \, [ m / \mathrm{min} ]$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;D 는 mm, N 은 rpm&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{3.14 \times 200 \times 3 {,} 600}{1 {,} 000}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;≒ 2,262&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;주의&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1,000 으로 나누는 것은 mm 를 m 로 바꾸기 위해&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>$$V = \dfrac{\pi D N}{1 {,} 000} = \dfrac{\pi \times 200 \times 3 {,} 600}{1 {,} 000} \fallingdotseq 2 {,} 262 \, m / \mathrm{min}$$&lt;div style="margin:12px 0 2px;font-weight:700"&gt;원주속도의 계산&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$V = \dfrac{\pi D N}{1 {,} 000} \, [ m / \mathrm{min} ]$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;D는 mm, N은 rpm&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{3.14 \times 200 \times 3 {,} 600}{1 {,} 000}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;≒ 2,262&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;주의&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1,000으로 나누는 것은 mm를 m로 바꾸기 위해&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH44" s="32" t="inlineStr">
         <is>
-          <t>① 452 는 계산과 맞지 않는다.&lt;br&gt;② 1258 도 그렇다.&lt;br&gt;③ 1856 도 그렇다.</t>
+          <t>① 452는 계산과 맞지 않는다.&lt;br&gt;② 1258 도 그렇다.&lt;br&gt;③ 1856 도 그렇다.</t>
         </is>
       </c>
       <c r="AI44" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;연삭기의 원주속도&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;πDN/1000&lt;/strong&gt;은 통째로 외운다 — &lt;strong&gt;200mm 는 0.2m 이니 0.2π × 3,600 ≒ 2,262&lt;/strong&gt;로 곧장 셈해도 같다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;원주속도 = πDN ÷ 1,000&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;연삭기의 원주속도&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;πDN/1000&lt;/strong&gt;은 통째로 외운다 — &lt;strong&gt;200mm는 0.2m 이니 0.2π × 3,600 ≒ 2,262&lt;/strong&gt;로 곧장 셈해도 같다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;원주속도 = πDN ÷ 1,000&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6994,17 +6998,17 @@
       </c>
       <c r="AG46" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;가드식 방호장치&lt;/strong&gt;가 hand in die 방식의 방호장치다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;Hand in die 와 No hand in die&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구분&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;방식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Hand in die&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;가드식 · 수인식 · 손쳐내기식 · 양수조작식 · 광전자식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;①&lt;/u&gt; · 손은 들어가되 다치지 않게&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;No hand in die&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안전울(방호울) · 안전금형 · 전용프레스 · 자동송급장치(자동프레스)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;②③④&lt;/u&gt; · 손이 못 들어간다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;가드식 방호장치&lt;/strong&gt;가 hand in die 방식의 방호장치다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;Hand in die와 No hand in die&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구분&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;방식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Hand in die&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;가드식 · 수인식 · 손쳐내기식 · 양수조작식 · 광전자식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;①&lt;/u&gt; · 손은 들어가되 다치지 않게&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;No hand in die&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안전울(방호울) · 안전금형 · 전용프레스 · 자동송급장치(자동프레스)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;②③④&lt;/u&gt; · 손이 못 들어간다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH46" s="32" t="inlineStr">
         <is>
-          <t>② 전용프레스의 도입은 no hand in die 다.&lt;br&gt;③ 자동프레스의 도입도 그렇다.&lt;br&gt;④ 안전울을 부착한 프레스도 그렇다.</t>
+          <t>② 전용프레스의 도입은 no hand in die다.&lt;br&gt;③ 자동프레스의 도입도 그렇다.&lt;br&gt;④ 안전울을 부착한 프레스도 그렇다.</t>
         </is>
       </c>
       <c r="AI46" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;프레스의 hand in die&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「금형 안에 손이 들어간다」는 전제 아래 다치지 않게 막는 장치&lt;/strong&gt;가 hand in die 다 — &lt;strong&gt;가드 · 수인 · 손쳐내기 · 양수조작 · 광전자&lt;/strong&gt; 다섯이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;가드식은 hand in die&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;프레스의 hand in die&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「금형 안에 손이 들어간다」는 전제 아래 다치지 않게 막는 장치&lt;/strong&gt;가 hand in die다 — &lt;strong&gt;가드 · 수인 · 손쳐내기 · 양수조작 · 광전자&lt;/strong&gt; 다섯이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;가드식은 hand in die&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -7907,7 +7911,7 @@
       </c>
       <c r="AI53" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;설비 진동의 종류&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;마모와 불균형은 「축이 한 바퀴 돌 때마다」 되풀이&lt;/strong&gt; 된다 — &lt;strong&gt;그래서 늘 같은 모양의 정상진동&lt;/strong&gt;이 된다. &lt;strong&gt;그 규칙성 덕분에 진동을 재어 고장을 미리 알아낼 수&lt;/strong&gt; 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;회전의 불균형에 의한 진동은 정상진동&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;설비 진동의 종류&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;마모와 불균형은 「축이 한 바퀴 돌 때마다」 되풀이&lt;/strong&gt;된다 — &lt;strong&gt;그래서 늘 같은 모양의 정상진동&lt;/strong&gt;이 된다. &lt;strong&gt;그 규칙성 덕분에 진동을 재어 고장을 미리 알아낼 수&lt;/strong&gt; 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;회전의 불균형에 의한 진동은 정상진동&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -8800,7 +8804,7 @@
       </c>
       <c r="AG60" s="32" t="inlineStr">
         <is>
-          <t>출제 당시 기준으로 승강기는 &lt;strong&gt;최대하중 0.25톤 이상&lt;/strong&gt; 이라야 양중기에 들었다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;양중기 5종&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;종류&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;크레인&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;호이스트 포함&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이동식 크레인&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;②&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;리프트&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이삿짐운반용은 적재하중 0.1톤 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;④&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;곤돌라&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;①&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;승강기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;출제 당시 최대하중 0.25톤 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.2톤은 못 미친다&lt;/u&gt; · ③&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>출제 당시 기준으로 승강기는 &lt;strong&gt;최대하중 0.25톤 이상&lt;/strong&gt;이라야 양중기에 들었다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;양중기 5종&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;종류&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;크레인&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;호이스트 포함&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이동식 크레인&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;②&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;리프트&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이삿짐운반용은 적재하중 0.1톤 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;④&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;곤돌라&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;①&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;승강기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;출제 당시 최대하중 0.25톤 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.2톤은 못 미친다&lt;/u&gt; · ③&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH60" s="32" t="inlineStr">
@@ -9068,7 +9072,7 @@
       </c>
       <c r="AI62" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;롤러기의 급정지장치&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「1.8 · 0.8 ~ 1.1 · 0.6」&lt;/strong&gt; 세 값이다 — &lt;strong&gt;0.8 은 복부의 아래 한계&lt;/strong&gt; 인데 그것을 무릎 자리에 옮겨 놓았다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;무릎 조작식은 0.6m 이내&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;롤러기의 급정지장치&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「1.8 · 0.8 ~ 1.1 · 0.6」&lt;/strong&gt; 세 값이다 — &lt;strong&gt;0.8은 복부의 아래 한계&lt;/strong&gt; 인데 그것을 무릎 자리에 옮겨 놓았다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;무릎 조작식은 0.6m 이내&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -9197,7 +9201,7 @@
       </c>
       <c r="AI63" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;허용접촉전압&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「2.5 · 25 · 50 · 제한 없음」&lt;/strong&gt; 네 칸이다 — &lt;strong&gt;앞의 둘이 10배 차이&lt;/strong&gt;라는 모양을 잡아 두면 0.5 로 바꿔 놓은 것이 보인다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;제1종 2.5V, 제2종 25V, 제3종 50V&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; 현행 한국전기설비규정(KEC)은 이 종별 구분을 두지 않고 계통접지 방식과 보호도체로 감전을 막도록 정하고 있다. 이 문항은 개정 전 기준으로 출제되어 ①이 정답으로 처리되었다.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;허용접촉전압&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「2.5 · 25 · 50 · 제한 없음」&lt;/strong&gt; 네 칸이다 — &lt;strong&gt;앞의 둘이 10배 차이&lt;/strong&gt;라는 모양을 잡아 두면 0.5로 바꿔 놓은 것이 보인다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;제1종 2.5V, 제2종 25V, 제3종 50V&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; 현행 한국전기설비규정(KEC)은 이 종별 구분을 두지 않고 계통접지 방식과 보호도체로 감전을 막도록 정하고 있다. 이 문항은 개정 전 기준으로 출제되어 ①이 정답으로 처리되었다.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -9316,7 +9320,7 @@
       </c>
       <c r="AG64" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;맨손으로 잡으면 구조자도 감전&lt;/strong&gt; 된다. &lt;strong&gt;먼저 전원을 끊거나 절연물로 떼어내야&lt;/strong&gt; 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;감전자 구출의 순서&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;순서&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;① 상황을 빠르게 판단하고 몸과 충전부의 접촉 여부를 확인한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;② 설비의 전원을 신속히 차단한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;가장 먼저 할 일&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;③ 전원을 끊을 수 없으면 절연 고무장갑·고무장화를 착용하고 마른 막대 등 절연물로 떼어낸다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;맨손으로 몸이나 손을 잡아 이탈시킨다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;구조자까지 감전된다&lt;/u&gt; · ③이 틀린 까닭&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;맨손으로 잡으면 구조자도 감전&lt;/strong&gt;된다. &lt;strong&gt;먼저 전원을 끊거나 절연물로 떼어내야&lt;/strong&gt; 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;감전자 구출의 순서&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;순서&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;① 상황을 빠르게 판단하고 몸과 충전부의 접촉 여부를 확인한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;② 설비의 전원을 신속히 차단한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;가장 먼저 할 일&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;③ 전원을 끊을 수 없으면 절연 고무장갑·고무장화를 착용하고 마른 막대 등 절연물로 떼어낸다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;맨손으로 몸이나 손을 잡아 이탈시킨다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;구조자까지 감전된다&lt;/u&gt; · ③이 틀린 까닭&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH64" s="32" t="inlineStr">
@@ -9574,12 +9578,12 @@
       </c>
       <c r="AG66" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;1분 이내&lt;/strong&gt;면 약 95% 를 살릴 수 있다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;응급처치 개시 시간과 소생률&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;개시 시간&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;소생률&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1분 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;95%&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2분 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;90%&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;3분 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;75%&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;4분 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;50%&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;5분 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;25%&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;6분 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;거의 0%&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;1분 이내&lt;/strong&gt;면 약 95%를 살릴 수 있다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;응급처치 개시 시간과 소생률&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;개시 시간&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;소생률&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1분 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;95%&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2분 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;90%&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;3분 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;75%&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;4분 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;50%&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;5분 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;25%&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;6분 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;거의 0%&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH66" s="32" t="inlineStr">
         <is>
-          <t>② 3분 이내면 약 75% 다.&lt;br&gt;③ 5분 이내면 약 25% 다.&lt;br&gt;④ 7분 이내면 거의 살리지 못한다.</t>
+          <t>② 3분 이내면 약 75%다.&lt;br&gt;③ 5분 이내면 약 25%다.&lt;br&gt;④ 7분 이내면 거의 살리지 못한다.</t>
         </is>
       </c>
       <c r="AI66" s="32" t="inlineStr">
@@ -9703,7 +9707,7 @@
       </c>
       <c r="AG67" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;인가전압이 클수록 피부저항은 크게 떨어진다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;피부 전기저항에 영향을 주는 것&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;조건&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;영향&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;인가전압의 크기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전압이 높을수록 저항이 뚝 떨어진다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt; · 절연 파괴&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;피부의 젖음&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;젖으면 1/12 ~ 1/20 로 떨어진다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;접촉면적과 압력&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;넓고 세게 누를수록 낮아진다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;통전시간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;길수록 낮아진다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;피부의 청결·노화&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;영향이 크지 않다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;인가전압이 클수록 피부저항은 크게 떨어진다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;피부 전기저항에 영향을 주는 것&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;조건&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;영향&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;인가전압의 크기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전압이 높을수록 저항이 뚝 떨어진다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt; · 절연 파괴&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;피부의 젖음&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;젖으면 1/12 ~ 1/20로 떨어진다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;접촉면적과 압력&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;넓고 세게 누를수록 낮아진다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;통전시간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;길수록 낮아진다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;피부의 청결·노화&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;영향이 크지 않다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH67" s="32" t="inlineStr">
@@ -9713,7 +9717,7 @@
       </c>
       <c r="AI67" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;인체의 전기저항&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;전압이 높아지면 피부의 각질층이 뚫려&lt;/strong&gt; 저항이 급격히 떨어진다 — &lt;strong&gt;500V 를 넘으면 거의 내부저항만 남는다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;인가전압이 클수록 피부저항이 떨어진다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;인체의 전기저항&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;전압이 높아지면 피부의 각질층이 뚫려&lt;/strong&gt; 저항이 급격히 떨어진다 — &lt;strong&gt;500V를 넘으면 거의 내부저항만 남는다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;인가전압이 클수록 피부저항이 떨어진다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -9963,7 +9967,7 @@
       </c>
       <c r="AI69" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;전압의 구분&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;고압이 「7,000V 이하」&lt;/strong&gt; 이니 특고압은 &lt;strong&gt;「7,000V 초과」&lt;/strong&gt; 라야 겹치지 않는다 — &lt;strong&gt;「이상」이면 7,000V 가 두 구분에 다 들어가 버린다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;특고압은 7,000V 초과&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;전압의 구분&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;고압이 「7,000V 이하」&lt;/strong&gt; 이니 특고압은 &lt;strong&gt;「7,000V 초과」&lt;/strong&gt;라야 겹치지 않는다 — &lt;strong&gt;「이상」이면 7,000V가 두 구분에 다 들어가 버린다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;특고압은 7,000V 초과&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10074,17 +10078,17 @@
       </c>
       <c r="AG70" s="32" t="inlineStr">
         <is>
-          <t>누설전류는 &lt;strong&gt;최대공급전류의 1/2,000 이하&lt;/strong&gt; 라야 한다.$200 \, A \times \dfrac{1}{2 {,} 000} = 0.1 \, A = 100 \, \mathrm{mA}$&lt;div style="margin:12px 0 2px;font-weight:700"&gt;누설전류의 한도&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;기준&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;최대공급전류의 1/2,000 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;200 ÷ 2,000 = 0.1 A&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;= 100 mA&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;단위&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 A = 1,000 mA&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;관련&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;저압 전로의 절연성능 판정에 쓴다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>누설전류는 &lt;strong&gt;최대공급전류의 1/2,000 이하&lt;/strong&gt;라야 한다.$200 \, A \times \dfrac{1}{2 {,} 000} = 0.1 \, A = 100 \, \mathrm{mA}$&lt;div style="margin:12px 0 2px;font-weight:700"&gt;누설전류의 한도&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;기준&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;최대공급전류의 1/2,000 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;200 ÷ 2,000 = 0.1 A&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;= 100 mA&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;단위&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 A = 1,000 mA&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;관련&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;저압 전로의 절연성능 판정에 쓴다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH70" s="32" t="inlineStr">
         <is>
-          <t>② 200mA 는 1/1,000 로 잡은 값이다.&lt;br&gt;③ 10mA 는 단위를 잘못 바꾼 값이다.&lt;br&gt;④ 20mA 도 그렇다.</t>
+          <t>② 200mA는 1/1,000로 잡은 값이다.&lt;br&gt;③ 10mA는 단위를 잘못 바꾼 값이다.&lt;br&gt;④ 20mA 도 그렇다.</t>
         </is>
       </c>
       <c r="AI70" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;누설전류의 한도&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;2,000 으로 나눈 뒤 A 를 mA 로 바꾸느라 1,000 을 곱한다&lt;/strong&gt; — &lt;strong&gt;결국 전류값의 절반(200 → 100)&lt;/strong&gt;이 되는 셈이라 계산이 간단하다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;누설전류는 최대공급전류의 1/2,000 이하&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;누설전류의 한도&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;2,000으로 나눈 뒤 A를 mA로 바꾸느라 1,000을 곱한다&lt;/strong&gt; — &lt;strong&gt;결국 전류값의 절반(200 → 100)&lt;/strong&gt;이 되는 셈이라 계산이 간단하다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;누설전류는 최대공급전류의 1/2,000 이하&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10332,17 +10336,17 @@
       </c>
       <c r="AG72" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;ⅡB 는 30mm&lt;/strong&gt;다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;플랜지 개구부에서 장애물까지의 최소 거리&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;가스 그룹&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;최소 거리&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;ⅡA&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;10 mm&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;프로판&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;ⅡB&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;30 mm&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;에틸렌&lt;/u&gt; · 이 문항&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;ⅡC&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;40 mm&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;수소 · 아세틸렌&lt;/u&gt; · 가장 위험&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;왜&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;빠져나온 뜨거운 가스가 장애물에 막히면 다시 뜨거워진다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;ⅡB는 30mm&lt;/strong&gt;다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;플랜지 개구부에서 장애물까지의 최소 거리&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;가스 그룹&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;최소 거리&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;ⅡA&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;10 mm&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;프로판&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;ⅡB&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;30 mm&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;에틸렌&lt;/u&gt; · 이 문항&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;ⅡC&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;40 mm&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;수소 · 아세틸렌&lt;/u&gt; · 가장 위험&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;왜&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;빠져나온 뜨거운 가스가 장애물에 막히면 다시 뜨거워진다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH72" s="32" t="inlineStr">
         <is>
-          <t>① 10mm 는 ⅡA 의 기준이다.&lt;br&gt;② 20mm 는 기준값이 아니다.&lt;br&gt;④ 40mm 는 ⅡC 의 기준이다.</t>
+          <t>① 10mm는 ⅡA의 기준이다.&lt;br&gt;② 20mm는 기준값이 아니다.&lt;br&gt;④ 40mm는 ⅡC의 기준이다.</t>
         </is>
       </c>
       <c r="AI72" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;내압방폭구조의 이격거리&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「10 · 30 · 40」&lt;/strong&gt; 세 값이다 — &lt;strong&gt;위험한 가스일수록 멀리 떼어 놓는다&lt;/strong&gt;는 방향만 잡으면 ⅡB 는 가운데다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;ⅡA 10, ⅡB 30, ⅡC 40 mm&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;내압방폭구조의 이격거리&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「10 · 30 · 40」&lt;/strong&gt; 세 값이다 — &lt;strong&gt;위험한 가스일수록 멀리 떼어 놓는다&lt;/strong&gt;는 방향만 잡으면 ⅡB는 가운데다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;ⅡA 10, ⅡB 30, ⅡC 40 mm&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10461,17 +10465,17 @@
       </c>
       <c r="AG73" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;T&lt;/strong&gt;다. &lt;strong&gt;Temperature 의 머리글자&lt;/strong&gt;다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;방폭기기의 온도등급&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;등급&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;최고표면온도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;T1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;450℃ 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;T2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;300℃ 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;T3&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;200℃ 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;T4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;135℃ 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;T5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;100℃ 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;T6&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;85℃ 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;가장 엄격&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;T&lt;/strong&gt;다. &lt;strong&gt;Temperature의 머리글자&lt;/strong&gt;다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;방폭기기의 온도등급&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;등급&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;최고표면온도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;T1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;450℃ 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;T2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;300℃ 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;T3&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;200℃ 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;T4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;135℃ 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;T5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;100℃ 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;T6&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;85℃ 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;가장 엄격&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH73" s="32" t="inlineStr">
         <is>
-          <t>① E 는 안전증 방폭구조의 기호다.&lt;br&gt;② S 는 온도등급 기호가 아니다.&lt;br&gt;④ N 은 비점화 방폭구조의 기호다.</t>
+          <t>① E는 안전증 방폭구조의 기호다.&lt;br&gt;② S는 온도등급 기호가 아니다.&lt;br&gt;④ N은 비점화 방폭구조의 기호다.</t>
         </is>
       </c>
       <c r="AI73" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;방폭기기의 온도등급&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;T 는 Temperature&lt;/strong&gt;다 — &lt;strong&gt;숫자가 커질수록 허용 표면온도가 낮아진다&lt;/strong&gt;는 것도 함께 잡아 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;온도등급은 T1 ~ T6&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;방폭기기의 온도등급&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;T는 Temperature&lt;/strong&gt;다 — &lt;strong&gt;숫자가 커질수록 허용 표면온도가 낮아진다&lt;/strong&gt;는 것도 함께 잡아 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;온도등급은 T1 ~ T6&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10590,7 +10594,7 @@
       </c>
       <c r="AG74" s="32" t="inlineStr">
         <is>
-          <t>$E = \dfrac{Q}{4 \pi \varepsilon_{0} \varepsilon_{s} r^{2}}$분모에 비유전율이 들어가므로 &lt;strong&gt;1/εs 로 작아진다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;매질에 따른 전계의 세기&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;진공에서&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$E = \dfrac{Q}{4 \pi \varepsilon_{0} r^{2}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;유전율 εs 인 매질에서&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$E = \dfrac{Q}{4 \pi \varepsilon_{0} \varepsilon_{s} r^{2}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1/εs 배&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;뜻&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;유전체가 전기장을 약하게 만든다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;분극&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;절연유의 비유전율&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;약 2 ~ 2.5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>$E = \dfrac{Q}{4 \pi \varepsilon_{0} \varepsilon_{s} r^{2}}$분모에 비유전율이 들어가므로 &lt;strong&gt;1/εs로 작아진다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;매질에 따른 전계의 세기&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;진공에서&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$E = \dfrac{Q}{4 \pi \varepsilon_{0} r^{2}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;유전율 εs 인 매질에서&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$E = \dfrac{Q}{4 \pi \varepsilon_{0} \varepsilon_{s} r^{2}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1/εs 배&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;뜻&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;유전체가 전기장을 약하게 만든다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;분극&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;절연유의 비유전율&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;약 2 ~ 2.5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH74" s="32" t="inlineStr">
@@ -10600,7 +10604,7 @@
       </c>
       <c r="AI74" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;유전체 속의 전계&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;유전체가 끼면 전기장이 약해진다&lt;/strong&gt; — &lt;strong&gt;그래서 절연물로 쓴다&lt;/strong&gt;. &lt;strong&gt;식에서 εs 가 분모에 있다&lt;/strong&gt;는 것만 기억하면 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;유전체 속에서 전계는 1/εs 로 작아진다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;유전체 속의 전계&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;유전체가 끼면 전기장이 약해진다&lt;/strong&gt; — &lt;strong&gt;그래서 절연물로 쓴다&lt;/strong&gt;. &lt;strong&gt;식에서 εs가 분모에 있다&lt;/strong&gt;는 것만 기억하면 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;유전체 속에서 전계는 1/εs로 작아진다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10729,7 +10733,7 @@
       </c>
       <c r="AI75" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;정전기의 축적&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;정전기가 쌓이려면 「빠져나갈 길이 없어야」&lt;/strong&gt; 한다 — &lt;strong&gt;금속은 길을 열어 주므로 쌓이지 않는다&lt;/strong&gt;. &lt;strong&gt;다만 「절연 격리된」 도체는 길이 끊겨 있어 쌓인다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;빠져나갈 길이 없어야 정전기가 쌓인다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;정전기의 축적&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;정전기가 쌓이려면 「빠져나갈 길이 없어야」&lt;/strong&gt;한다 — &lt;strong&gt;금속은 길을 열어 주므로 쌓이지 않는다&lt;/strong&gt;. &lt;strong&gt;다만 「절연 격리된」 도체는 길이 끊겨 있어 쌓인다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;빠져나갈 길이 없어야 정전기가 쌓인다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10853,7 +10857,7 @@
       </c>
       <c r="AH76" s="32" t="inlineStr">
         <is>
-          <t>② A-B-E-Y 는 순서가 어긋난다.&lt;br&gt;③ Y-E-B-A 도 그렇다.&lt;br&gt;④ B-Y-A-E 도 그렇다.</t>
+          <t>② A-B-E-Y는 순서가 어긋난다.&lt;br&gt;③ Y-E-B-A 도 그렇다.&lt;br&gt;④ B-Y-A-E 도 그렇다.</t>
         </is>
       </c>
       <c r="AI76" s="32" t="inlineStr">
@@ -10943,7 +10947,7 @@
       </c>
       <c r="U77" s="32" t="inlineStr">
         <is>
-          <t>충격전압시험시의 표준충격파형을 1.2×50㎲로 나타내는 경우 1.2 와 50 이 뜻하는 것은?</t>
+          <t>충격전압시험시의 표준충격파형을 1.2×50㎲로 나타내는 경우 1.2와 50이 뜻하는 것은?</t>
         </is>
       </c>
       <c r="V77" s="32" t="inlineStr"/>
@@ -10977,7 +10981,7 @@
       </c>
       <c r="AG77" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;1.2㎲ 는 파두장, 50㎲ 는 파미장&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;표준충격파형 1.2 × 50㎲&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;파두장&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.2 ㎲&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0 에서 파고값까지 오르는 시간&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;파미장&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;50 ㎲&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;파고값의 절반으로 떨어질 때까지의 시간&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;허용오차&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;파두장 ±30%, 파미장 ±20%&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;쓰임&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;낙뢰를 흉내 낸 파형으로 절연내력을 시험한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;1.2㎲ 는 파두장, 50㎲ 는 파미장&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;표준충격파형 1.2 × 50㎲&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;파두장&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.2 ㎲&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0에서 파고값까지 오르는 시간&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;파미장&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;50 ㎲&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;파고값의 절반으로 떨어질 때까지의 시간&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;허용오차&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;파두장 ±30%, 파미장 ±20%&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;쓰임&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;낙뢰를 흉내 낸 파형으로 절연내력을 시험한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH77" s="32" t="inlineStr">
@@ -11235,7 +11239,7 @@
       </c>
       <c r="AG79" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;접지선에는 차단기를 달지 않는다&lt;/strong&gt;. &lt;strong&gt;끊기면 접지가 사라져 오히려 위험&lt;/strong&gt; 하다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;과전류 차단장치를 달 수 없는 곳&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;대상&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;접지공사의 접지도체&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;끊기면 접지가 없어진다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;다선식 전로의 중성선&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;각 극이 동시에 차단되는 경우는 예외&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;저압 가공전선로의 접지측 전선&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;전압선 · 인입선&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;차단장치를 단다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;접지선에는 차단기를 달지 않는다&lt;/strong&gt;. &lt;strong&gt;끊기면 접지가 사라져 오히려 위험&lt;/strong&gt;하다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;과전류 차단장치를 달 수 없는 곳&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;대상&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;접지공사의 접지도체&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;끊기면 접지가 없어진다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;다선식 전로의 중성선&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;각 극이 동시에 차단되는 경우는 예외&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;저압 가공전선로의 접지측 전선&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;전압선 · 인입선&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;차단장치를 단다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH79" s="32" t="inlineStr">
@@ -11503,7 +11507,7 @@
       </c>
       <c r="AI81" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;제전기의 제전효과&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;제전은 「이온을 만들어 대전물체에 보내는」 일&lt;/strong&gt;이다 — &lt;strong&gt;얼마나 많이 만드나 · 어디에 두나 · 상대가 어떻게 대전돼 있나&lt;/strong&gt; 셋이 좌우한다. &lt;strong&gt;전선 길이는 그 어디에도 끼지 않는다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;전원의 극성과 전선 길이는 제전효과와 무관&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;제전기의 제전효과&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;제전은 「이온을 만들어 대전물체에 보내는」일&lt;/strong&gt;이다 — &lt;strong&gt;얼마나 많이 만드나 · 어디에 두나 · 상대가 어떻게 대전돼 있나&lt;/strong&gt; 셋이 좌우한다. &lt;strong&gt;전선 길이는 그 어디에도 끼지 않는다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;전원의 극성과 전선 길이는 제전효과와 무관&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -11755,7 +11759,7 @@
       </c>
       <c r="AG83" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;마르면 스스로 열을 내며 분해·폭발&lt;/strong&gt; 하므로 &lt;strong&gt;알코올로 적셔&lt;/strong&gt; 둔다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;니트로셀룰로오스(질화면)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;분류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;제5류 위험물 — 자기반응성 물질&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;질산에스테르류&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위험&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;건조 상태에서 자연발열 → 분해 폭발&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;저장&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;에틸알코올이나 이소프로필알코올로 습면&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;물 또는 알코올로 20% 이상 적신다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;성질&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;분자 안에 산소를 품고 있어 공기가 없어도 탄다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;마르면 스스로 열을 내며 분해·폭발&lt;/strong&gt;하므로 &lt;strong&gt;알코올로 적셔&lt;/strong&gt; 둔다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;니트로셀룰로오스(질화면)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;분류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;제5류 위험물 — 자기반응성 물질&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;질산에스테르류&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위험&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;건조 상태에서 자연발열 → 분해 폭발&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;저장&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;에틸알코올이나 이소프로필알코올로 습면&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;물 또는 알코올로 20% 이상 적신다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;성질&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;분자 안에 산소를 품고 있어 공기가 없어도 탄다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH83" s="32" t="inlineStr">
@@ -11876,7 +11880,7 @@
       </c>
       <c r="AG84" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;「잘 견디는 사람을 배치」&lt;/strong&gt; 하는 것은 &lt;strong&gt;유해물을 그대로 두는&lt;/strong&gt; 것이라 대책이 아니다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;유해물 취급의 안전대책&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구분&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;대책&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;발생원 대책&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;유해물 발생원의 봉쇄 · 유해물이나 공정의 변경 · 대체&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;②③&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;전파경로 대책&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;작업공정의 밀폐 · 작업장의 격리 · 국소배기 · 전체환기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;④&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;수용자 대책&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;보호구 착용 · 작업시간 단축 · 교육&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;작업적응자의 배치&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;유해물은 그대로 남는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;대책이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;「잘 견디는 사람을 배치」&lt;/strong&gt;하는 것은 &lt;strong&gt;유해물을 그대로 두는&lt;/strong&gt; 것이라 대책이 아니다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;유해물 취급의 안전대책&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구분&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;대책&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;발생원 대책&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;유해물 발생원의 봉쇄 · 유해물이나 공정의 변경 · 대체&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;②③&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;전파경로 대책&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;작업공정의 밀폐 · 작업장의 격리 · 국소배기 · 전체환기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;④&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;수용자 대책&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;보호구 착용 · 작업시간 단축 · 교육&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;작업적응자의 배치&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;유해물은 그대로 남는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;대책이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH84" s="32" t="inlineStr">
@@ -12139,7 +12143,7 @@
       </c>
       <c r="AH86" s="32" t="inlineStr">
         <is>
-          <t>① 메탄은 약 0.28mJ 로 가장 크다.&lt;br&gt;② 프로판은 약 0.26mJ 다.&lt;br&gt;③ 벤젠은 약 0.20mJ 다.</t>
+          <t>① 메탄은 약 0.28mJ로 가장 크다.&lt;br&gt;② 프로판은 약 0.26mJ다.&lt;br&gt;③ 벤젠은 약 0.20mJ다.</t>
         </is>
       </c>
       <c r="AI86" s="32" t="inlineStr">
@@ -12263,7 +12267,7 @@
       </c>
       <c r="AG87" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;아세틸렌&lt;/strong&gt;이다. &lt;strong&gt;그대로 압축하면 저절로 분해 폭발&lt;/strong&gt; 하므로 아세톤에 녹여 담는다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;아세틸렌의 저장&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;왜 그냥 못 담나&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.5기압 이상으로 압축하면 분해 폭발한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;어떻게 담나&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;아세톤이나 DMF 에 녹여 다공성 물질에 스며들게 한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;다공질 물질&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;규조토 · 석면 · 목탄 · 산화철 · 다공성 플라스틱&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;용해도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;아세톤 1L 에 아세틸렌 약 25L 가 녹는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;15기압에서는 375L&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;사용 압력&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;게이지 압력 127kPa 초과 금지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;아세틸렌&lt;/strong&gt;이다. &lt;strong&gt;그대로 압축하면 저절로 분해 폭발&lt;/strong&gt;하므로 아세톤에 녹여 담는다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;아세틸렌의 저장&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;왜 그냥 못 담나&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.5기압 이상으로 압축하면 분해 폭발한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;어떻게 담나&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;아세톤이나 DMF에 녹여 다공성 물질에 스며들게 한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;다공질 물질&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;규조토 · 석면 · 목탄 · 산화철 · 다공성 플라스틱&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;용해도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;아세톤 1L에 아세틸렌 약 25L가 녹는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;15기압에서는 375L&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;사용 압력&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;게이지 압력 127kPa 초과 금지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH87" s="32" t="inlineStr">
@@ -12273,7 +12277,7 @@
       </c>
       <c r="AI87" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;아세틸렌의 저장&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;아세틸렌만 「녹여서」 담는다&lt;/strong&gt; — &lt;strong&gt;다른 가스는 그냥 눌러 담아도 되지만 아세틸렌은 눌리는 것 자체가 위험&lt;/strong&gt; 하다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;아세틸렌은 아세톤에 녹여 다공질에 담는다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;아세틸렌의 저장&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;아세틸렌만 「녹여서」 담는다&lt;/strong&gt; — &lt;strong&gt;다른 가스는 그냥 눌러 담아도 되지만 아세틸렌은 눌리는 것 자체가 위험&lt;/strong&gt;하다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;아세틸렌은 아세톤에 녹여 다공질에 담는다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12401,12 +12405,12 @@
       </c>
       <c r="AH88" s="32" t="inlineStr">
         <is>
-          <t>① CO 가 H₂ 보다 넓지 않다.&lt;br&gt;③ C₃H₈ 이 가장 넓은 것도 아니다.&lt;br&gt;④ CH₄ 가 H₂ 보다 넓은 것도 아니다.</t>
+          <t>① CO가 H₂ 보다 넓지 않다.&lt;br&gt;③ C₃H₈ 이 가장 넓은 것도 아니다.&lt;br&gt;④ CH₄ 가 H₂ 보다 넓은 것도 아니다.</t>
         </is>
       </c>
       <c r="AI88" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;가스의 폭발범위&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;상한이 70을 넘는 것은 수소와 일산화탄소 둘&lt;/strong&gt; 뿐이다 — &lt;strong&gt;그 둘이 앞자리를 차지하고, 하한이 낮은 수소가 첫째&lt;/strong&gt;다. &lt;strong&gt;메탄과 프로판은 한참 좁다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;H₂ &amp;gt; CO &amp;gt; CH₄ &amp;gt; C₃H₈&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;가스의 폭발범위&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;상한이 70을 넘는 것은 수소와 일산화탄소 둘&lt;/strong&gt;뿐이다 — &lt;strong&gt;그 둘이 앞자리를 차지하고, 하한이 낮은 수소가 첫째&lt;/strong&gt;다. &lt;strong&gt;메탄과 프로판은 한참 좁다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;H₂ &amp;gt; CO &amp;gt; CH₄ &amp;gt; C₃H₈&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12534,12 @@
       </c>
       <c r="AH89" s="32" t="inlineStr">
         <is>
-          <t>① 0.25 는 계산과 맞지 않는다.&lt;br&gt;② 0.36 도 그렇다.&lt;br&gt;④ 0.58 도 그렇다.</t>
+          <t>① 0.25는 계산과 맞지 않는다.&lt;br&gt;② 0.36 도 그렇다.&lt;br&gt;④ 0.58 도 그렇다.</t>
         </is>
       </c>
       <c r="AI89" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;함수율&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;단위 「kg·H₂O / kg」의 아래쪽 kg 이 「건조 고체」&lt;/strong&gt;라는 뜻이다 — &lt;strong&gt;나누는 쪽이 6.8, 10 이 아니다&lt;/strong&gt;. &lt;strong&gt;10 으로 나누면 0.32 로 보기에 없다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;함수율 = 수분 무게 ÷ 건조 고체 무게&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;함수율&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;단위 「kg·H₂O / kg」의 아래쪽 kg이 「건조 고체」&lt;/strong&gt;라는 뜻이다 — &lt;strong&gt;나누는 쪽이 6.8, 10이 아니다&lt;/strong&gt;. &lt;strong&gt;10으로 나누면 0.32로 보기에 없다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;함수율 = 수분 무게 ÷ 건조 고체 무게&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -13051,7 +13055,7 @@
       </c>
       <c r="AI93" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;발열반응과 흡열반응&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;공기 속 질소와 산소가 그냥 반응하지 않는 것&lt;/strong&gt;은 흡열이기 때문이다 — &lt;strong&gt;번개나 엔진의 고온에서만 NO 가 생긴다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;질소와 산소의 반응은 흡열&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;발열반응과 흡열반응&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;공기 속 질소와 산소가 그냥 반응하지 않는 것&lt;/strong&gt;은 흡열이기 때문이다 — &lt;strong&gt;번개나 엔진의 고온에서만 NO가 생긴다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;질소와 산소의 반응은 흡열&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -13299,7 +13303,7 @@
       </c>
       <c r="AG95" s="32" t="inlineStr">
         <is>
-          <t>변경 사유가 생기면 &lt;strong&gt;지체 없이 보완&lt;/strong&gt; 한다. &lt;strong&gt;「14일 이내 승인」이라는 절차는 없다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;공정안전보고서의 절차&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;절차&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;작성 시 산업안전보건위원회의 심의를 거친다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위원회가 없으면 근로자대표의 의견을 듣는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;변경 사유가 생기면 지체 없이 보완한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「14일 이내 승인」이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;고용노동부장관은 이행 상태를 정기적으로 평가한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;보완 상태가 불량하면 다시 제출하도록 명할 수 있다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>변경 사유가 생기면 &lt;strong&gt;지체 없이 보완&lt;/strong&gt;한다. &lt;strong&gt;「14일 이내 승인」이라는 절차는 없다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;공정안전보고서의 절차&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;절차&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;작성 시 산업안전보건위원회의 심의를 거친다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위원회가 없으면 근로자대표의 의견을 듣는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;변경 사유가 생기면 지체 없이 보완한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「14일 이내 승인」이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;고용노동부장관은 이행 상태를 정기적으로 평가한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;보완 상태가 불량하면 다시 제출하도록 명할 수 있다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH95" s="32" t="inlineStr">
@@ -13433,7 +13437,7 @@
       </c>
       <c r="AH96" s="32" t="inlineStr">
         <is>
-          <t>② CH₃COCH₃ 은 아세톤으로 인화성 액체다.&lt;br&gt;③ n-C₃H₇OH 는 프로필알코올로 인화성 액체다.&lt;br&gt;④ C₂H₅OC₂H₅ 는 디에틸에테르로 특수인화물이다.</t>
+          <t>② CH₃COCH₃ 은 아세톤으로 인화성 액체다.&lt;br&gt;③ n-C₃H₇OH는 프로필알코올로 인화성 액체다.&lt;br&gt;④ C₂H₅OC₂H₅ 는 디에틸에테르로 특수인화물이다.</t>
         </is>
       </c>
       <c r="AI96" s="32" t="inlineStr">
@@ -13567,7 +13571,7 @@
       </c>
       <c r="AI97" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;공정안전보고서의 구성&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「자료 · 평가 · 운전 · 비상」 네 덩이&lt;/strong&gt; 뿐이다 — &lt;strong&gt;「안전율」은 기계설계의 낱말&lt;/strong&gt;이라 여기 끼지 않는다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;공정안전자료·위험성평가서·안전운전계획·비상조치계획&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;공정안전보고서의 구성&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「자료 · 평가 · 운전 · 비상」 네 덩이&lt;/strong&gt;뿐이다 — &lt;strong&gt;「안전율」은 기계설계의 낱말&lt;/strong&gt;이라 여기 끼지 않는다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;공정안전자료·위험성평가서·안전운전계획·비상조치계획&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -13696,7 +13700,7 @@
       </c>
       <c r="AI98" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;강화액 소화약제&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;물의 단점은 「겨울에 언다」와 「소화력이 약하다」&lt;/strong&gt; 둘이다 — &lt;strong&gt;탄산칼륨을 녹이면 어는점이 내려가고 소화력도 세진다&lt;/strong&gt; 해서 「강화액」이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;물에 탄산칼륨을 녹인 것이 강화액&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;강화액 소화약제&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;물의 단점은 「겨울에 언다」와 「소화력이 약하다」&lt;/strong&gt; 둘이다 — &lt;strong&gt;탄산칼륨을 녹이면 어는점이 내려가고 소화력도 세진다&lt;/strong&gt;해서 「강화액」이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;물에 탄산칼륨을 녹인 것이 강화액&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -13820,7 +13824,7 @@
       </c>
       <c r="AH99" s="32" t="inlineStr">
         <is>
-          <t>① Flame arrester 는 화염의 전파를 막는 장치다.&lt;br&gt;② Vent stack 은 압력을 대기로 내보내는 설비다.&lt;br&gt;③ 긴급방출장치는 내용물을 빼내는 설비다.</t>
+          <t>① Flame arrester는 화염의 전파를 막는 장치다.&lt;br&gt;② Vent stack은 압력을 대기로 내보내는 설비다.&lt;br&gt;③ 긴급방출장치는 내용물을 빼내는 설비다.</t>
         </is>
       </c>
       <c r="AI99" s="32" t="inlineStr">
@@ -13944,7 +13948,7 @@
       </c>
       <c r="AG100" s="32" t="inlineStr">
         <is>
-          <t>충전(充塡) 방폭구조는 &lt;strong&gt;q&lt;/strong&gt;다. &lt;strong&gt;n 은 비점화 방폭구조&lt;/strong&gt;다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;방폭구조의 기호&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기호&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구조&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;d&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;내압 방폭구조&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;p&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;압력 방폭구조&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;o&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;유입 방폭구조&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;e&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안전증 방폭구조&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;①&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;ia, ib&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;본질안전 방폭구조&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;②&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;m&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;몰드(캡슐) 방폭구조&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;③&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;q&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;충전 방폭구조&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「n」이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;n&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;비점화 방폭구조&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;2종 장소 전용&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>충전(充塡) 방폭구조는 &lt;strong&gt;q&lt;/strong&gt;다. &lt;strong&gt;n은 비점화 방폭구조&lt;/strong&gt;다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;방폭구조의 기호&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기호&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구조&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;d&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;내압 방폭구조&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;p&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;압력 방폭구조&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;o&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;유입 방폭구조&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;e&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안전증 방폭구조&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;①&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;ia, ib&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;본질안전 방폭구조&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;②&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;m&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;몰드(캡슐) 방폭구조&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;③&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;q&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;충전 방폭구조&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「n」이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;n&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;비점화 방폭구조&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;2종 장소 전용&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH100" s="32" t="inlineStr">
@@ -14718,7 +14722,7 @@
       </c>
       <c r="AG106" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;스크레이퍼&lt;/strong&gt;다. &lt;strong&gt;파고 · 싣고 · 나르고 · 펴는 일을 한 대로&lt;/strong&gt; 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;차량계 건설기계&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;스크레이퍼&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;굴착·적재·운반·흙깔기를 한 대로 연속 수행&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;대규모 정지작업&lt;/u&gt; · 이 문항&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;크램쉘&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;좁고 깊은 곳을 움켜쥐어 판다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;우물통 · 수직굴&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;로우더&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;쌓인 흙을 퍼서 싣는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;불도저&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;흙을 밀어 옮긴다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;짧은 거리&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;스크레이퍼&lt;/strong&gt;다. &lt;strong&gt;파고 · 싣고 · 나르고 · 펴는 일을 한 대로&lt;/strong&gt;한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;차량계 건설기계&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;스크레이퍼&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;굴착·적재·운반·흙깔기를 한 대로 연속 수행&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;대규모 정지작업&lt;/u&gt; · 이 문항&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;크램쉘&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;좁고 깊은 곳을 움켜쥐어 판다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;우물통 · 수직굴&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;로우더&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;쌓인 흙을 퍼서 싣는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;불도저&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;흙을 밀어 옮긴다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;짧은 거리&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH106" s="32" t="inlineStr">
@@ -14976,7 +14980,7 @@
       </c>
       <c r="AG108" s="32" t="inlineStr">
         <is>
-          <t>파이프서포트는 &lt;strong&gt;높이 3.5m 를 초과하면 2m 이내마다&lt;/strong&gt; 수평연결재를 둔다. &lt;strong&gt;「4.5m」가 아니다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;거푸집동바리의 설치기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;파이프서포트는 3개 이상 이어 쓰지 않는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이어서 쓸 때는 4개 이상의 볼트나 전용철물로 잇는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;높이가 3.5m 를 초과하면 높이 2m 이내마다 2개 방향으로 수평연결재&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「4.5m」가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;침하 방지를 위해 깔목·콘크리트 타설·말뚝박기 등을 한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;강재와 강재의 접속부는 볼트나 클램프 등 전용철물로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;강관틀 동바리는 강관틀 사이에 교차가새를 설치한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>파이프서포트는 &lt;strong&gt;높이 3.5m를 초과하면 2m 이내마다&lt;/strong&gt; 수평연결재를 둔다. &lt;strong&gt;「4.5m」가 아니다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;거푸집동바리의 설치기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;파이프서포트는 3개 이상 이어 쓰지 않는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이어서 쓸 때는 4개 이상의 볼트나 전용철물로 잇는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;높이가 3.5m를 초과하면 높이 2m 이내마다 2개 방향으로 수평연결재&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「4.5m」가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;침하 방지를 위해 깔목·콘크리트 타설·말뚝박기 등을 한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;강재와 강재의 접속부는 볼트나 클램프 등 전용철물로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;강관틀 동바리는 강관틀 사이에 교차가새를 설치한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH108" s="32" t="inlineStr">
@@ -14986,7 +14990,7 @@
       </c>
       <c r="AI108" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;거푸집동바리의 설치&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「3.5m 초과면 2m 마다」&lt;/strong&gt;라는 짝을 통째로 외운다 — &lt;strong&gt;4.5m 로 늘려 놓으면 그 사이 구간이 무방비&lt;/strong&gt;가 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;파이프서포트 3.5m 초과면 2m 이내마다 수평연결재&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;거푸집동바리의 설치&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「3.5m 초과면 2m 마다」&lt;/strong&gt;라는 짝을 통째로 외운다 — &lt;strong&gt;4.5m로 늘려 놓으면 그 사이 구간이 무방비&lt;/strong&gt;가 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;파이프서포트 3.5m 초과면 2m 이내마다 수평연결재&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -15207,7 +15211,11 @@
           <t>다음 설명에서 제시된 산업안전보건법에서 말하는 고용노동부령으로 정하는 공사에 해당하지 않는 것은?</t>
         </is>
       </c>
-      <c r="V110" s="32" t="inlineStr"/>
+      <c r="V110" s="32" t="inlineStr">
+        <is>
+          <t>건설업 중 고용노동부령으로 정하는 공사를 착공하려는 사업주는 고용노동부령으로 정하는 자격을 갖춘 자의 의견을 들은 후 유해·위험방지계획서를 작성하여 고용노동부령으로 정하는 바에 따라 고용노동부장관에게 제출하여야 한다.</t>
+        </is>
+      </c>
       <c r="W110" s="32" t="inlineStr"/>
       <c r="X110" s="32" t="inlineStr">
         <is>
@@ -15238,7 +15246,7 @@
       </c>
       <c r="AG110" s="32" t="inlineStr">
         <is>
-          <t>굴착공사는 &lt;strong&gt;깊이 10m 이상&lt;/strong&gt; 이라야 대상이다. &lt;strong&gt;8m 는 못 미친다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;건설공사 유해위험방지계획서 제출 대상&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;대상공사&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지상높이 31m 이상인 건축물 또는 인공구조물의 건설·개조·해체&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;연면적 3만m² 이상인 건축물 또는 5천m² 이상의 문화·집회시설 등&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;최대 지간길이 50m 이상인 교량건설 등의 공사&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;터널 건설 등의 공사&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;다목적댐·발전용댐 및 저수용량 2천만톤 이상의 용수전용댐&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;깊이 10m 이상인 굴착공사&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「8m」는 대상이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>굴착공사는 &lt;strong&gt;깊이 10m 이상&lt;/strong&gt;이라야 대상이다. &lt;strong&gt;8m는 못 미친다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;건설공사 유해위험방지계획서 제출 대상&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;대상공사&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지상높이 31m 이상인 건축물 또는 인공구조물의 건설·개조·해체&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;연면적 3만m² 이상인 건축물 또는 5천m² 이상의 문화·집회시설 등&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;최대 지간길이 50m 이상인 교량건설 등의 공사&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;터널 건설 등의 공사&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;다목적댐·발전용댐 및 저수용량 2천만톤 이상의 용수전용댐&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;깊이 10m 이상인 굴착공사&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「8m」는 대상이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH110" s="32" t="inlineStr">
@@ -15248,7 +15256,7 @@
       </c>
       <c r="AI110" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;유해위험방지계획서 제출 대상공사&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「31m · 50m · 10m · 3만m²」&lt;/strong&gt; 네 수다 — &lt;strong&gt;굴착은 10m&lt;/strong&gt;라 8m 는 한 칸 모자란다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;굴착공사는 깊이 10m 이상&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;유해위험방지계획서 제출 대상공사&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「31m · 50m · 10m · 3만m²」&lt;/strong&gt; 네 수다 — &lt;strong&gt;굴착은 10m&lt;/strong&gt;라 8m는 한 칸 모자란다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;굴착공사는 깊이 10m 이상&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -15500,17 +15508,17 @@
       </c>
       <c r="AG112" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;1.5m 를 초과&lt;/strong&gt; 하면 통행 설비를 설치한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;하역작업의 안전기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;선창 내부의 통행설비&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;갑판 윗면에서 선창 밑바닥까지 1.5m 초과 시&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;부두·안벽의 통로 폭&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;90cm 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;화물자동차의 승강설비&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;짐 윗면까지 2m 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;단위화물 100kg 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;작업지휘자 지정&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;1.5m를 초과&lt;/strong&gt;하면 통행 설비를 설치한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;하역작업의 안전기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;선창 내부의 통행설비&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;갑판 윗면에서 선창 밑바닥까지 1.5m 초과 시&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;부두·안벽의 통로 폭&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;90cm 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;화물자동차의 승강설비&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;짐 윗면까지 2m 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;단위화물 100kg 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;작업지휘자 지정&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH112" s="32" t="inlineStr">
         <is>
-          <t>① 1.3m 는 기준값이 아니다.&lt;br&gt;③ 1.8m 도 그렇다.&lt;br&gt;④ 2.0m 는 화물자동차 승강설비의 기준이다.</t>
+          <t>① 1.3m는 기준값이 아니다.&lt;br&gt;③ 1.8m 도 그렇다.&lt;br&gt;④ 2.0m는 화물자동차 승강설비의 기준이다.</t>
         </is>
       </c>
       <c r="AI112" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;선창 내부의 통행설비&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;1.5m 는 「뛰어내리기에는 이미 위험한」 깊이&lt;/strong&gt;다 — &lt;strong&gt;굴착작업의 승강설비 기준(1.5m)과 같은 값&lt;/strong&gt;이라 함께 외운다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;선창 깊이 1.5m 초과면 통행설비&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;선창 내부의 통행설비&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;1.5m는 「뛰어내리기에는 이미 위험한」 깊이&lt;/strong&gt;다 — &lt;strong&gt;굴착작업의 승강설비 기준(1.5m)과 같은 값&lt;/strong&gt;이라 함께 외운다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;선창 깊이 1.5m 초과면 통행설비&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -15892,7 +15900,7 @@
       </c>
       <c r="AH115" s="32" t="inlineStr">
         <is>
-          <t>② Road Roller 는 다짐기계다.&lt;br&gt;③ Shovel loader 는 적재기계다.&lt;br&gt;④ Belt conveyer 는 운반기계다.</t>
+          <t>② Road Roller는 다짐기계다.&lt;br&gt;③ Shovel loader는 적재기계다.&lt;br&gt;④ Belt conveyer는 운반기계다.</t>
         </is>
       </c>
       <c r="AI115" s="32" t="inlineStr">
@@ -16278,17 +16286,17 @@
       </c>
       <c r="AG118" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;100kg 이상&lt;/strong&gt;의 하중에 견뎌야 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전난간의 구조 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;하중&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;가장 취약한 지점·방향에서 100kg 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;상부난간대&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;바닥면에서 90cm 이상 120cm 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;120cm 를 넘으면 60cm 이내마다 중간난간대&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;중간난간대&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;상부난간대와 바닥면의 중간에&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;발끝막이판&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;바닥면에서 10cm 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;난간대&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;지름 2.7cm 이상의 금속제 파이프 등&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;100kg 이상&lt;/strong&gt;의 하중에 견뎌야 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전난간의 구조 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;하중&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;가장 취약한 지점·방향에서 100kg 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;상부난간대&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;바닥면에서 90cm 이상 120cm 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;120cm를 넘으면 60cm 이내마다 중간난간대&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;중간난간대&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;상부난간대와 바닥면의 중간에&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;발끝막이판&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;바닥면에서 10cm 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;난간대&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;지름 2.7cm 이상의 금속제 파이프 등&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH118" s="32" t="inlineStr">
         <is>
-          <t>① 80kg 은 기준값이 아니다.&lt;br&gt;③ 120kg 도 그렇다.&lt;br&gt;④ 150kg 도 그렇다.</t>
+          <t>① 80kg은 기준값이 아니다.&lt;br&gt;③ 120kg 도 그렇다.&lt;br&gt;④ 150kg 도 그렇다.</t>
         </is>
       </c>
       <c r="AI118" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전난간의 구조&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「100kg · 90 ~ 120cm · 10cm · 2.7cm」&lt;/strong&gt; 네 값이다 — &lt;strong&gt;100kg 은 어른 한 사람이 기대는 무게&lt;/strong&gt; 라고 생각하면 외우기 쉽다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;안전난간은 100kg 이상의 하중에 견딜 것&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;안전난간의 구조&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「100kg · 90 ~ 120cm · 10cm · 2.7cm」&lt;/strong&gt; 네 값이다 — &lt;strong&gt;100kg은 어른 한 사람이 기대는 무게&lt;/strong&gt; 라고 생각하면 외우기 쉽다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;안전난간은 100kg 이상의 하중에 견딜 것&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
